--- a/artfynd/A 40720-2022 artfynd.xlsx
+++ b/artfynd/A 40720-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,415 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120334594</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>353</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Järvfljotberget, Älvdalens skjutfält, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>430017</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6818046</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Lars Ambrosiusson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120334595</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79131</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Järvfljotberget, Älvdalens skjutfält, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>430059</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6818155</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Lars Ambrosiusson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120334598</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79131</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Järvfljotberget, Älvdalens skjutfält, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>430040</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6818237</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Lars Ambrosiusson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120334592</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78187</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>353</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Järvfljotberget, Älvdalens skjutfält, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>430015</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6818183</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Hindemo, Lars Ambrosiusson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40720-2022 artfynd.xlsx
+++ b/artfynd/A 40720-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334594</v>
+        <v>120334595</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430017</v>
+        <v>430059</v>
       </c>
       <c r="R3" t="n">
-        <v>6818046</v>
+        <v>6818155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334595</v>
+        <v>120334592</v>
       </c>
       <c r="B4" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430059</v>
+        <v>430015</v>
       </c>
       <c r="R4" t="n">
-        <v>6818155</v>
+        <v>6818183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,6 +978,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334598</v>
+        <v>120334594</v>
       </c>
       <c r="B5" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430040</v>
+        <v>430017</v>
       </c>
       <c r="R5" t="n">
-        <v>6818237</v>
+        <v>6818046</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120334592</v>
+        <v>120334598</v>
       </c>
       <c r="B6" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430015</v>
+        <v>430040</v>
       </c>
       <c r="R6" t="n">
-        <v>6818183</v>
+        <v>6818237</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1183,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40720-2022 artfynd.xlsx
+++ b/artfynd/A 40720-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334595</v>
+        <v>120334592</v>
       </c>
       <c r="B3" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430059</v>
+        <v>430015</v>
       </c>
       <c r="R3" t="n">
-        <v>6818155</v>
+        <v>6818183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +876,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334592</v>
+        <v>120334594</v>
       </c>
       <c r="B4" t="n">
         <v>78187</v>
@@ -934,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430015</v>
+        <v>430017</v>
       </c>
       <c r="R4" t="n">
-        <v>6818183</v>
+        <v>6818046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +979,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334594</v>
+        <v>120334598</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430017</v>
+        <v>430040</v>
       </c>
       <c r="R5" t="n">
-        <v>6818046</v>
+        <v>6818237</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120334598</v>
+        <v>120334595</v>
       </c>
       <c r="B6" t="n">
         <v>79131</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430040</v>
+        <v>430059</v>
       </c>
       <c r="R6" t="n">
-        <v>6818237</v>
+        <v>6818155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 40720-2022 artfynd.xlsx
+++ b/artfynd/A 40720-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334592</v>
+        <v>120334598</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430015</v>
+        <v>430040</v>
       </c>
       <c r="R3" t="n">
-        <v>6818183</v>
+        <v>6818237</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334594</v>
+        <v>120334595</v>
       </c>
       <c r="B4" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430017</v>
+        <v>430059</v>
       </c>
       <c r="R4" t="n">
-        <v>6818046</v>
+        <v>6818155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334598</v>
+        <v>120334592</v>
       </c>
       <c r="B5" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430040</v>
+        <v>430015</v>
       </c>
       <c r="R5" t="n">
-        <v>6818237</v>
+        <v>6818183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,6 +1080,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120334595</v>
+        <v>120334594</v>
       </c>
       <c r="B6" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430059</v>
+        <v>430017</v>
       </c>
       <c r="R6" t="n">
-        <v>6818155</v>
+        <v>6818046</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 40720-2022 artfynd.xlsx
+++ b/artfynd/A 40720-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334598</v>
+        <v>120334592</v>
       </c>
       <c r="B3" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430040</v>
+        <v>430015</v>
       </c>
       <c r="R3" t="n">
-        <v>6818237</v>
+        <v>6818183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +876,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -996,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334592</v>
+        <v>120334594</v>
       </c>
       <c r="B5" t="n">
         <v>78187</v>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430015</v>
+        <v>430017</v>
       </c>
       <c r="R5" t="n">
-        <v>6818183</v>
+        <v>6818046</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1081,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120334594</v>
+        <v>120334598</v>
       </c>
       <c r="B6" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430017</v>
+        <v>430040</v>
       </c>
       <c r="R6" t="n">
-        <v>6818046</v>
+        <v>6818237</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 40720-2022 artfynd.xlsx
+++ b/artfynd/A 40720-2022 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334592</v>
+        <v>120334595</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430015</v>
+        <v>430059</v>
       </c>
       <c r="R3" t="n">
-        <v>6818183</v>
+        <v>6818155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334595</v>
+        <v>120334594</v>
       </c>
       <c r="B4" t="n">
-        <v>79131</v>
+        <v>78187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430059</v>
+        <v>430017</v>
       </c>
       <c r="R4" t="n">
-        <v>6818155</v>
+        <v>6818046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334594</v>
+        <v>120334592</v>
       </c>
       <c r="B5" t="n">
         <v>78187</v>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430017</v>
+        <v>430015</v>
       </c>
       <c r="R5" t="n">
-        <v>6818046</v>
+        <v>6818183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,6 +1080,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40720-2022 artfynd.xlsx
+++ b/artfynd/A 40720-2022 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334595</v>
+        <v>120334598</v>
       </c>
       <c r="B3" t="n">
         <v>79131</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430059</v>
+        <v>430040</v>
       </c>
       <c r="R3" t="n">
-        <v>6818155</v>
+        <v>6818237</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334594</v>
+        <v>120334592</v>
       </c>
       <c r="B4" t="n">
         <v>78187</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430017</v>
+        <v>430015</v>
       </c>
       <c r="R4" t="n">
-        <v>6818046</v>
+        <v>6818183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,6 +978,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334592</v>
+        <v>120334594</v>
       </c>
       <c r="B5" t="n">
         <v>78187</v>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430015</v>
+        <v>430017</v>
       </c>
       <c r="R5" t="n">
-        <v>6818183</v>
+        <v>6818046</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1081,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120334598</v>
+        <v>120334595</v>
       </c>
       <c r="B6" t="n">
         <v>79131</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430040</v>
+        <v>430059</v>
       </c>
       <c r="R6" t="n">
-        <v>6818237</v>
+        <v>6818155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 40720-2022 artfynd.xlsx
+++ b/artfynd/A 40720-2022 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120334598</v>
+        <v>120334595</v>
       </c>
       <c r="B3" t="n">
         <v>79131</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430040</v>
+        <v>430059</v>
       </c>
       <c r="R3" t="n">
-        <v>6818237</v>
+        <v>6818155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120334592</v>
+        <v>120334594</v>
       </c>
       <c r="B4" t="n">
         <v>78187</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430015</v>
+        <v>430017</v>
       </c>
       <c r="R4" t="n">
-        <v>6818183</v>
+        <v>6818046</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120334594</v>
+        <v>120334592</v>
       </c>
       <c r="B5" t="n">
         <v>78187</v>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430017</v>
+        <v>430015</v>
       </c>
       <c r="R5" t="n">
-        <v>6818046</v>
+        <v>6818183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,6 +1080,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120334595</v>
+        <v>120334598</v>
       </c>
       <c r="B6" t="n">
         <v>79131</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430059</v>
+        <v>430040</v>
       </c>
       <c r="R6" t="n">
-        <v>6818155</v>
+        <v>6818237</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
